--- a/data/projects/70e5ca737ae5433e9f0f3134d216acf7/早期介入/交付预案/输出结果/智算部件配置信息表.xlsx
+++ b/data/projects/70e5ca737ae5433e9f0f3134d216acf7/早期介入/交付预案/输出结果/智算部件配置信息表.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,6 +469,33 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="inlineStr"/>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>V2.2_20260614213043_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr"/>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>V2.2_20260614213043_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr"/>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>V2.2_20260614213043_DRB</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/projects/70e5ca737ae5433e9f0f3134d216acf7/早期介入/交付预案/输出结果/智算部件配置信息表.xlsx
+++ b/data/projects/70e5ca737ae5433e9f0f3134d216acf7/早期介入/交付预案/输出结果/智算部件配置信息表.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -496,6 +496,33 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr"/>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>V2.3_20260614220356_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr"/>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>V2.3_20260614220356_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr"/>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>V2.3_20260614220356_DRB</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/projects/70e5ca737ae5433e9f0f3134d216acf7/早期介入/交付预案/输出结果/智算部件配置信息表.xlsx
+++ b/data/projects/70e5ca737ae5433e9f0f3134d216acf7/早期介入/交付预案/输出结果/智算部件配置信息表.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -523,6 +523,33 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="inlineStr"/>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>V2.4_20260615171738_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr"/>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>V2.4_20260615171738_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr"/>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>V2.4_20260615171738_DRB</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
